--- a/artfynd/A 25516-2021 artfynd.xlsx
+++ b/artfynd/A 25516-2021 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119436100</v>
+        <v>119435936</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>802120</v>
+        <v>802091</v>
       </c>
       <c r="R3" t="n">
-        <v>7236174</v>
+        <v>7236287</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119435936</v>
+        <v>119436100</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>802091</v>
+        <v>802120</v>
       </c>
       <c r="R4" t="n">
-        <v>7236287</v>
+        <v>7236174</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 25516-2021 artfynd.xlsx
+++ b/artfynd/A 25516-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>119435751</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>90728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,14 +718,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finnträsk, Nb</t>
+          <t>Kältjärnen, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>802154</v>
+        <v>802091</v>
       </c>
       <c r="R2" t="n">
-        <v>7236238</v>
+        <v>7236287</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -778,7 +778,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -788,7 +788,7 @@
         <v>119435936</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,14 +828,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Finnträsk, Nb</t>
+          <t>Kältjärnen, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>802091</v>
+        <v>802154</v>
       </c>
       <c r="R3" t="n">
-        <v>7236287</v>
+        <v>7236238</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +888,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -898,7 +898,7 @@
         <v>119436100</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>90746</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Finnträsk, Nb</t>
+          <t>Kältjärnen, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -998,10 +998,350 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Patrik Nygren, Sirirat Chanon</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121876650</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90739</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kältjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>802097</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7236305</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på gammal grov asp</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Patrik Nygren</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren, Sirirat Chanon</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121876701</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78642</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kältjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>802114</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7236228</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren, Sirirat Chanon</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121876761</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57373</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kältjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>802162</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7236255</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren, Sirirat Chanon</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25516-2021 artfynd.xlsx
+++ b/artfynd/A 25516-2021 artfynd.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Sirirat Chanon, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Sirirat Chanon</t>
+          <t>Sirirat Chanon, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 25516-2021 artfynd.xlsx
+++ b/artfynd/A 25516-2021 artfynd.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sirirat Chanon, Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sirirat Chanon, Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 25516-2021 artfynd.xlsx
+++ b/artfynd/A 25516-2021 artfynd.xlsx
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121876650</v>
+        <v>121876761</v>
       </c>
       <c r="B5" t="n">
-        <v>90739</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,34 +1017,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1052,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>802097</v>
+        <v>802162</v>
       </c>
       <c r="R5" t="n">
-        <v>7236305</v>
+        <v>7236255</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1093,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på gammal grov asp</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,7 +1102,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121876761</v>
+        <v>121876650</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>90739</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,35 +1242,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1278,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>802162</v>
+        <v>802097</v>
       </c>
       <c r="R7" t="n">
-        <v>7236255</v>
+        <v>7236305</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1317,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>hack i gran</t>
+          <t>på gammal grov asp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,6 +1326,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25516-2021 artfynd.xlsx
+++ b/artfynd/A 25516-2021 artfynd.xlsx
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121876761</v>
+        <v>121876650</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>90739</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,35 +1017,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1053,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>802162</v>
+        <v>802097</v>
       </c>
       <c r="R5" t="n">
-        <v>7236255</v>
+        <v>7236305</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1092,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hack i gran</t>
+          <t>på gammal grov asp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,6 +1101,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121876701</v>
+        <v>121876761</v>
       </c>
       <c r="B6" t="n">
-        <v>78642</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,34 +1132,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>802114</v>
+        <v>802162</v>
       </c>
       <c r="R6" t="n">
-        <v>7236228</v>
+        <v>7236255</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,13 +1206,17 @@
           <t>2024-08-25</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1230,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121876650</v>
+        <v>121876701</v>
       </c>
       <c r="B7" t="n">
-        <v>90739</v>
+        <v>78642</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,27 +1251,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1205</v>
+        <v>6434</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1277,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>802097</v>
+        <v>802114</v>
       </c>
       <c r="R7" t="n">
-        <v>7236305</v>
+        <v>7236228</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,11 +1318,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>på gammal grov asp</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 25516-2021 artfynd.xlsx
+++ b/artfynd/A 25516-2021 artfynd.xlsx
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121876650</v>
+        <v>121876761</v>
       </c>
       <c r="B5" t="n">
-        <v>90790</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,34 +1017,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1052,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>802097</v>
+        <v>802162</v>
       </c>
       <c r="R5" t="n">
-        <v>7236305</v>
+        <v>7236255</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1093,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på gammal grov asp</t>
+          <t>hack i gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,7 +1102,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121876761</v>
+        <v>121876701</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>78671</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,35 +1132,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1168,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>802162</v>
+        <v>802114</v>
       </c>
       <c r="R6" t="n">
-        <v>7236255</v>
+        <v>7236228</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,17 +1205,13 @@
           <t>2024-08-25</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1235,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121876701</v>
+        <v>121876650</v>
       </c>
       <c r="B7" t="n">
-        <v>78671</v>
+        <v>90790</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,27 +1246,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6434</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1282,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>802114</v>
+        <v>802097</v>
       </c>
       <c r="R7" t="n">
-        <v>7236228</v>
+        <v>7236305</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,6 +1315,11 @@
           <t>2024-08-25</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>på gammal grov asp</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sirirat Chanon, Patrik Nygren</t>
+          <t>Patrik Nygren, Sirirat Chanon</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 25516-2021 artfynd.xlsx
+++ b/artfynd/A 25516-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1343,6 +1343,507 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127273578</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91615</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>658</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>kältjärnen2, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>802127</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7236205</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # grov # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127273572</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91677</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>kältjärnen1, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>802151</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7236247</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Svamp, fruktkropp mm</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Fungi, fruit bodies, etc. # på ullticka på grov granlåga # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127273579</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91319</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>kältjärnen1, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>802151</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7236247</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # grov # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127273571</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91319</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>kältjärnen2, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>802127</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7236205</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # grov # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25516-2021 artfynd.xlsx
+++ b/artfynd/A 25516-2021 artfynd.xlsx
@@ -1348,7 +1348,7 @@
         <v>127273578</v>
       </c>
       <c r="B8" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127273572</v>
       </c>
       <c r="B9" t="n">
-        <v>91677</v>
+        <v>91683</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>127273579</v>
       </c>
       <c r="B10" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>127273571</v>
       </c>
       <c r="B11" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 25516-2021 artfynd.xlsx
+++ b/artfynd/A 25516-2021 artfynd.xlsx
@@ -1348,7 +1348,7 @@
         <v>127273578</v>
       </c>
       <c r="B8" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127273572</v>
       </c>
       <c r="B9" t="n">
-        <v>91683</v>
+        <v>91684</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>127273579</v>
       </c>
       <c r="B10" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>127273571</v>
       </c>
       <c r="B11" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 25516-2021 artfynd.xlsx
+++ b/artfynd/A 25516-2021 artfynd.xlsx
@@ -1348,7 +1348,7 @@
         <v>127273578</v>
       </c>
       <c r="B8" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127273572</v>
       </c>
       <c r="B9" t="n">
-        <v>91684</v>
+        <v>91688</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>127273579</v>
       </c>
       <c r="B10" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>127273571</v>
       </c>
       <c r="B11" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 25516-2021 artfynd.xlsx
+++ b/artfynd/A 25516-2021 artfynd.xlsx
@@ -1348,7 +1348,7 @@
         <v>127273578</v>
       </c>
       <c r="B8" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127273572</v>
       </c>
       <c r="B9" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>127273579</v>
       </c>
       <c r="B10" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>127273571</v>
       </c>
       <c r="B11" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 25516-2021 artfynd.xlsx
+++ b/artfynd/A 25516-2021 artfynd.xlsx
@@ -1348,7 +1348,7 @@
         <v>127273578</v>
       </c>
       <c r="B8" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127273572</v>
       </c>
       <c r="B9" t="n">
-        <v>91690</v>
+        <v>91696</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>127273579</v>
       </c>
       <c r="B10" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>127273571</v>
       </c>
       <c r="B11" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 25516-2021 artfynd.xlsx
+++ b/artfynd/A 25516-2021 artfynd.xlsx
@@ -1348,7 +1348,7 @@
         <v>127273578</v>
       </c>
       <c r="B8" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127273572</v>
       </c>
       <c r="B9" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>127273579</v>
       </c>
       <c r="B10" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>127273571</v>
       </c>
       <c r="B11" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 25516-2021 artfynd.xlsx
+++ b/artfynd/A 25516-2021 artfynd.xlsx
@@ -1348,7 +1348,7 @@
         <v>127273578</v>
       </c>
       <c r="B8" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127273572</v>
       </c>
       <c r="B9" t="n">
-        <v>91699</v>
+        <v>91707</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>127273579</v>
       </c>
       <c r="B10" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>127273571</v>
       </c>
       <c r="B11" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 25516-2021 artfynd.xlsx
+++ b/artfynd/A 25516-2021 artfynd.xlsx
@@ -1348,7 +1348,7 @@
         <v>127273578</v>
       </c>
       <c r="B8" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127273572</v>
       </c>
       <c r="B9" t="n">
-        <v>91707</v>
+        <v>91708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>127273579</v>
       </c>
       <c r="B10" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>127273571</v>
       </c>
       <c r="B11" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 25516-2021 artfynd.xlsx
+++ b/artfynd/A 25516-2021 artfynd.xlsx
@@ -1348,7 +1348,7 @@
         <v>127273578</v>
       </c>
       <c r="B8" t="n">
-        <v>91646</v>
+        <v>91615</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>127273572</v>
       </c>
       <c r="B9" t="n">
-        <v>91708</v>
+        <v>91677</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>127273579</v>
       </c>
       <c r="B10" t="n">
-        <v>91350</v>
+        <v>91319</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>127273571</v>
       </c>
       <c r="B11" t="n">
-        <v>91350</v>
+        <v>91319</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
